--- a/港岛-渣甸山及黄泥涌峡-皇第/皇第_销控明细表.xlsx
+++ b/港岛-渣甸山及黄泥涌峡-皇第/皇第_销控明细表.xlsx
@@ -763,7 +763,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -899,7 +899,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2020-06-08</t>
+          <t>2020-06-09</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -965,7 +965,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2020-06-08</t>
+          <t>2020-06-09</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2020-06-22</t>
+          <t>2020-06-23</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2021-08-17</t>
+          <t>2021-08-18</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2020-08-22</t>
+          <t>2020-08-23</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2021-09-02</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2020-02-06</t>
+          <t>2020-02-07</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2020-09-08</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2020-05-14</t>
+          <t>2020-05-15</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2020-06-29</t>
+          <t>2020-06-30</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2022-05-22</t>
+          <t>2022-05-23</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2023-02-07</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1918,7 +1918,7 @@
           <t>A | 6673呎 (4+房)
 $42000万
 $62,940/呎
-(25年-11月-12日)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -1950,7 +1950,7 @@
           <t>A | 2848呎 (3房)
 $21930万
 $77,000/呎
-(20年-06月-08日)</t>
+(20年-06月-09日)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr"/>
@@ -1966,7 +1966,7 @@
           <t>A | 2761呎 (3房)
 $21930万
 $79,426/呎
-(20年-06月-08日)</t>
+(20年-06月-09日)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr"/>
@@ -1982,7 +1982,7 @@
           <t>A | 2761呎 (3房)
 $22214万
 $80,458/呎
-(20年-06月-22日)</t>
+(20年-06月-23日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr"/>
@@ -1998,7 +1998,7 @@
           <t>A | 2761呎 (3房)
 $20561万
 $74,470/呎
-(21年-08月-17日)</t>
+(21年-08月-18日)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr"/>
@@ -2030,7 +2030,7 @@
           <t>A | 2760呎 (2房)
 $20000万
 $72,464/呎
-(20年-08月-22日)</t>
+(20年-08月-23日)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr"/>
@@ -2047,7 +2047,7 @@
           <t>B | 2763呎 (2房)
 $18500万
 $66,956/呎
-(21年-09月-01日)</t>
+(21年-09月-02日)</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2062,7 @@
           <t>A | 2846呎 (3房)
 $17645万
 $62,000/呎
-(20年-02月-06日)</t>
+(20年-02月-07日)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr"/>
@@ -2079,7 +2079,7 @@
           <t>B | 2763呎 (3房)
 $16800万
 $60,803/呎
-(20年-09月-08日)</t>
+(20年-09月-09日)</t>
         </is>
       </c>
     </row>
@@ -2094,7 +2094,7 @@
           <t>A | 2760呎 (3房)
 $16800万
 $60,870/呎
-(20年-05月-14日)</t>
+(20年-05月-15日)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr"/>
@@ -2111,7 +2111,7 @@
           <t>B | 2849呎 (3房)
 $17200万
 $60,372/呎
-(20年-06月-29日)</t>
+(20年-06月-30日)</t>
         </is>
       </c>
     </row>
@@ -2126,7 +2126,7 @@
           <t>A | 3976呎 (3房)
 $21200万
 $53,320/呎
-(24年-10月-21日)</t>
+(24年-10月-22日)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr"/>
@@ -2142,7 +2142,7 @@
           <t>A | 4102呎 (3房)
 $28714万
 $70,000/呎
-(23年-02月-06日)</t>
+(23年-02月-07日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -2150,7 +2150,7 @@
           <t>B | 4075呎 (3房)
 $33424万
 $82,022/呎
-(22年-05月-22日)</t>
+(22年-05月-23日)</t>
         </is>
       </c>
     </row>
